--- a/diseases/d008/1995-1999.xlsx
+++ b/diseases/d008/1995-1999.xlsx
@@ -1943,6 +1943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2550,6 +2555,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2926,6 +2936,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3302,6 +3317,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3678,6 +3698,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4054,6 +4079,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4430,6 +4460,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4806,6 +4841,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5182,6 +5222,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5558,6 +5603,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5934,6 +5984,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6310,6 +6365,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7076,6 +7136,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7683,6 +7748,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8059,6 +8129,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8435,6 +8510,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8811,6 +8891,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9187,6 +9272,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9563,6 +9653,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9939,6 +10034,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10315,6 +10415,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10691,6 +10796,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11067,6 +11177,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11443,6 +11558,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12209,6 +12329,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12816,6 +12941,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13192,6 +13322,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13568,6 +13703,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13944,6 +14084,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14320,6 +14465,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14696,6 +14846,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15072,6 +15227,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15448,6 +15608,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15824,6 +15989,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16200,6 +16370,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16574,6 +16749,11 @@
       <c r="S85" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">

--- a/diseases/d008/1995-1999.xlsx
+++ b/diseases/d008/1995-1999.xlsx
@@ -1938,6 +1938,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1950,13 +1955,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2535,6 +2550,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2547,13 +2567,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2901,6 +2931,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2913,13 +2948,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3267,6 +3312,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3279,13 +3329,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3633,6 +3693,11 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3645,13 +3710,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3999,6 +4074,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4011,13 +4091,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4365,6 +4455,11 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4377,13 +4472,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4731,6 +4836,11 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4743,13 +4853,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5097,6 +5217,11 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5109,13 +5234,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5463,6 +5598,11 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5475,13 +5615,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5829,6 +5979,11 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5841,13 +5996,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6195,6 +6360,11 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6207,13 +6377,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6951,6 +7131,11 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6963,13 +7148,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7548,6 +7743,11 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7560,13 +7760,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7914,6 +8124,11 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7926,13 +8141,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8280,6 +8505,11 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8292,13 +8522,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8646,6 +8886,11 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8658,13 +8903,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9012,6 +9267,11 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9024,13 +9284,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9378,6 +9648,11 @@
       <c r="Q48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9390,13 +9665,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9744,6 +10029,11 @@
       <c r="Q50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9756,13 +10046,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10110,6 +10410,11 @@
       <c r="Q52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10122,13 +10427,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10476,6 +10791,11 @@
       <c r="Q54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10488,13 +10808,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10842,6 +11172,11 @@
       <c r="Q56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10854,13 +11189,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11208,6 +11553,11 @@
       <c r="Q58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11220,13 +11570,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11964,6 +12324,11 @@
       <c r="Q62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11976,13 +12341,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12561,6 +12936,11 @@
       <c r="Q65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12573,13 +12953,23 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12927,6 +13317,11 @@
       <c r="Q67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12939,13 +13334,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13293,6 +13698,11 @@
       <c r="Q69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13305,13 +13715,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13659,6 +14079,11 @@
       <c r="Q71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13671,13 +14096,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14025,6 +14460,11 @@
       <c r="Q73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14037,13 +14477,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14391,6 +14841,11 @@
       <c r="Q75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14403,13 +14858,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14757,6 +15222,11 @@
       <c r="Q77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14769,13 +15239,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15123,6 +15603,11 @@
       <c r="Q79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15135,13 +15620,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15489,6 +15984,11 @@
       <c r="Q81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15501,13 +16001,23 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15855,6 +16365,11 @@
       <c r="Q83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15867,13 +16382,23 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -16221,6 +16746,11 @@
       <c r="Q85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16233,12 +16763,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
